--- a/Hydroacoustics/Fillet/Fillet BlueView Filenames List.xlsx
+++ b/Hydroacoustics/Fillet/Fillet BlueView Filenames List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khomolka\Documents\GitHub\PGST-Natural-Resources\Hydroacoustics\Fillet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D12F1ED-EC4F-4852-B32B-4C297C940877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7144F19-5EB1-4657-86C3-16D0A0DDE6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B7532181-221C-4FDC-AE64-D05EB76F1E45}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B7532181-221C-4FDC-AE64-D05EB76F1E45}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4435" uniqueCount="4435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4438" uniqueCount="4438">
   <si>
     <t>Apr_04_2023_140648.son</t>
   </si>
@@ -13341,6 +13341,15 @@
   </si>
   <si>
     <t>Apr_21_2023_162708_888.son</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>File Timestamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fillet Status </t>
   </si>
 </sst>
 </file>
@@ -13692,19 +13701,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE42DAA-C731-4191-9894-313C6077B12A}">
-  <dimension ref="A1:B4430"/>
+  <dimension ref="A1:D4430"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.85546875" customWidth="1"/>
-    <col min="2" max="2" width="96.5703125" customWidth="1"/>
+    <col min="2" max="2" width="97.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>4435</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4436</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4437</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -13712,72 +13732,72 @@
         <v>302</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
